--- a/files/Clientes.xlsx
+++ b/files/Clientes.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BrunoColantonio\Desktop\BRUNO\Fenix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colan\OneDrive\Escritorio\BRUNO\Fenix\Fenix\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E83C1-72CF-41D3-83E0-0ECD0AF47928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECB3C3D-EA83-467F-8F2B-7B85CA944158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1050" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="339">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -1616,6 +1627,45 @@
   </si>
   <si>
     <t>ABEL-VICKY</t>
+  </si>
+  <si>
+    <t>VILLARES</t>
+  </si>
+  <si>
+    <t>FERRETERA MALU</t>
+  </si>
+  <si>
+    <t>CORRALÓN EL TANO</t>
+  </si>
+  <si>
+    <t>HÉCTOR ACOSTA</t>
+  </si>
+  <si>
+    <t>LOS ACACIOS</t>
+  </si>
+  <si>
+    <t>FERRETERíA JORGITO</t>
+  </si>
+  <si>
+    <t>LOS 4 HERMANOS</t>
+  </si>
+  <si>
+    <t>FERRETERÍA COLON</t>
+  </si>
+  <si>
+    <t>FERRETERÍA LOZANO</t>
+  </si>
+  <si>
+    <t>FERRETERÍA MC</t>
+  </si>
+  <si>
+    <t>ELECTRO FER CASEY</t>
+  </si>
+  <si>
+    <t>MARCOS PAZ</t>
+  </si>
+  <si>
+    <t>LAS HERAS</t>
   </si>
 </sst>
 </file>
@@ -1639,7 +1689,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1667,6 +1717,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1698,7 +1754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1733,6 +1789,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2014,16 +2078,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D234"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D244"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.88671875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="42.36328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.90625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2037,7 +2101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2051,7 +2115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -2065,7 +2129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -2079,7 +2143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -2093,7 +2157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -2107,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -2121,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -2135,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -2149,7 +2213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -2163,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -2177,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
@@ -2191,7 +2255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
@@ -2205,7 +2269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -2219,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
@@ -2233,7 +2297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2247,7 +2311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -2261,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -2275,7 +2339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -2289,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
@@ -2303,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -2317,7 +2381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
@@ -2331,7 +2395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
@@ -2345,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
@@ -2359,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
@@ -2373,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -2387,7 +2451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>42</v>
       </c>
@@ -2401,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>44</v>
       </c>
@@ -2415,7 +2479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
@@ -2429,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
@@ -2443,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -2457,7 +2521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -2471,7 +2535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>52</v>
       </c>
@@ -2485,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>53</v>
       </c>
@@ -2499,7 +2563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>54</v>
       </c>
@@ -2513,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>55</v>
       </c>
@@ -2527,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>56</v>
       </c>
@@ -2541,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>57</v>
       </c>
@@ -2555,7 +2619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>58</v>
       </c>
@@ -2569,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>59</v>
       </c>
@@ -2583,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>227</v>
       </c>
@@ -2597,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>61</v>
       </c>
@@ -2611,7 +2675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>63</v>
       </c>
@@ -2625,7 +2689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>65</v>
       </c>
@@ -2639,7 +2703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>66</v>
       </c>
@@ -2653,7 +2717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>67</v>
       </c>
@@ -2667,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>68</v>
       </c>
@@ -2681,7 +2745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>69</v>
       </c>
@@ -2695,7 +2759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>70</v>
       </c>
@@ -2709,7 +2773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>71</v>
       </c>
@@ -2723,7 +2787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>72</v>
       </c>
@@ -2737,7 +2801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>73</v>
       </c>
@@ -2751,7 +2815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>74</v>
       </c>
@@ -2765,7 +2829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>75</v>
       </c>
@@ -2779,7 +2843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>76</v>
       </c>
@@ -2793,7 +2857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>77</v>
       </c>
@@ -2807,7 +2871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>238</v>
       </c>
@@ -2821,7 +2885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>239</v>
       </c>
@@ -2835,7 +2899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>240</v>
       </c>
@@ -2849,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>78</v>
       </c>
@@ -2863,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>79</v>
       </c>
@@ -2877,7 +2941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>80</v>
       </c>
@@ -2891,7 +2955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>81</v>
       </c>
@@ -2905,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>82</v>
       </c>
@@ -2919,7 +2983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>249</v>
       </c>
@@ -2933,7 +2997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>84</v>
       </c>
@@ -2947,7 +3011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>85</v>
       </c>
@@ -2961,7 +3025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>250</v>
       </c>
@@ -2975,7 +3039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>251</v>
       </c>
@@ -2989,7 +3053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>282</v>
       </c>
@@ -3003,7 +3067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>86</v>
       </c>
@@ -3017,7 +3081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>255</v>
       </c>
@@ -3031,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>256</v>
       </c>
@@ -3045,7 +3109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>257</v>
       </c>
@@ -3059,7 +3123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>258</v>
       </c>
@@ -3073,7 +3137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>87</v>
       </c>
@@ -3087,7 +3151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>259</v>
       </c>
@@ -3101,7 +3165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>260</v>
       </c>
@@ -3115,7 +3179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>261</v>
       </c>
@@ -3129,7 +3193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>262</v>
       </c>
@@ -3143,7 +3207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>263</v>
       </c>
@@ -3157,7 +3221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>88</v>
       </c>
@@ -3171,7 +3235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>264</v>
       </c>
@@ -3185,7 +3249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>265</v>
       </c>
@@ -3199,7 +3263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>266</v>
       </c>
@@ -3213,7 +3277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>267</v>
       </c>
@@ -3227,7 +3291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>268</v>
       </c>
@@ -3241,7 +3305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>269</v>
       </c>
@@ -3255,7 +3319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>270</v>
       </c>
@@ -3269,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>271</v>
       </c>
@@ -3283,7 +3347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
         <v>89</v>
       </c>
@@ -3297,7 +3361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>91</v>
       </c>
@@ -3311,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="8" t="s">
         <v>92</v>
       </c>
@@ -3325,7 +3389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="8" t="s">
         <v>93</v>
       </c>
@@ -3339,7 +3403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>94</v>
       </c>
@@ -3353,7 +3417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
         <v>95</v>
       </c>
@@ -3367,7 +3431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
         <v>97</v>
       </c>
@@ -3381,7 +3445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
         <v>98</v>
       </c>
@@ -3395,7 +3459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>99</v>
       </c>
@@ -3409,7 +3473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="8" t="s">
         <v>100</v>
       </c>
@@ -3423,7 +3487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>188</v>
       </c>
@@ -3437,7 +3501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
         <v>233</v>
       </c>
@@ -3451,7 +3515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
         <v>101</v>
       </c>
@@ -3465,7 +3529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
         <v>293</v>
       </c>
@@ -3479,7 +3543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="8" t="s">
         <v>102</v>
       </c>
@@ -3493,7 +3557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
         <v>104</v>
       </c>
@@ -3507,7 +3571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="8" t="s">
         <v>105</v>
       </c>
@@ -3521,7 +3585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>106</v>
       </c>
@@ -3535,7 +3599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
         <v>22</v>
       </c>
@@ -3549,7 +3613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
         <v>107</v>
       </c>
@@ -3563,7 +3627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
         <v>108</v>
       </c>
@@ -3577,7 +3641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="8" t="s">
         <v>109</v>
       </c>
@@ -3591,7 +3655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="8" t="s">
         <v>110</v>
       </c>
@@ -3605,7 +3669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="8" t="s">
         <v>230</v>
       </c>
@@ -3617,7 +3681,7 @@
       </c>
       <c r="D114" s="8"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
         <v>111</v>
       </c>
@@ -3631,7 +3695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="8" t="s">
         <v>103</v>
       </c>
@@ -3645,7 +3709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>112</v>
       </c>
@@ -3659,7 +3723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>113</v>
       </c>
@@ -3673,7 +3737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>114</v>
       </c>
@@ -3687,7 +3751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
         <v>115</v>
       </c>
@@ -3701,7 +3765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>116</v>
       </c>
@@ -3715,7 +3779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="9" t="s">
         <v>117</v>
       </c>
@@ -3729,7 +3793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>118</v>
       </c>
@@ -3743,7 +3807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
         <v>119</v>
       </c>
@@ -3757,7 +3821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>120</v>
       </c>
@@ -3771,7 +3835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
         <v>121</v>
       </c>
@@ -3785,7 +3849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>122</v>
       </c>
@@ -3799,7 +3863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
         <v>123</v>
       </c>
@@ -3813,7 +3877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>124</v>
       </c>
@@ -3827,7 +3891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="9" t="s">
         <v>125</v>
       </c>
@@ -3841,7 +3905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>127</v>
       </c>
@@ -3855,7 +3919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>128</v>
       </c>
@@ -3869,7 +3933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>129</v>
       </c>
@@ -3883,7 +3947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>130</v>
       </c>
@@ -3897,7 +3961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>131</v>
       </c>
@@ -3911,7 +3975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>132</v>
       </c>
@@ -3925,7 +3989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>159</v>
       </c>
@@ -3939,7 +4003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>160</v>
       </c>
@@ -3953,7 +4017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>161</v>
       </c>
@@ -3967,7 +4031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="9" t="s">
         <v>186</v>
       </c>
@@ -3981,7 +4045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>160</v>
       </c>
@@ -3995,7 +4059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="9" t="s">
         <v>162</v>
       </c>
@@ -4009,7 +4073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>135</v>
       </c>
@@ -4023,7 +4087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="9" t="s">
         <v>136</v>
       </c>
@@ -4037,7 +4101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>137</v>
       </c>
@@ -4051,7 +4115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>138</v>
       </c>
@@ -4065,7 +4129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>139</v>
       </c>
@@ -4079,7 +4143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>140</v>
       </c>
@@ -4093,7 +4157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>141</v>
       </c>
@@ -4107,7 +4171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>142</v>
       </c>
@@ -4121,7 +4185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>143</v>
       </c>
@@ -4135,7 +4199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="9" t="s">
         <v>144</v>
       </c>
@@ -4149,7 +4213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="9" t="s">
         <v>145</v>
       </c>
@@ -4163,7 +4227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="9" t="s">
         <v>146</v>
       </c>
@@ -4177,7 +4241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="9" t="s">
         <v>147</v>
       </c>
@@ -4191,7 +4255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="9" t="s">
         <v>148</v>
       </c>
@@ -4205,7 +4269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="9" t="s">
         <v>149</v>
       </c>
@@ -4219,7 +4283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="9" t="s">
         <v>150</v>
       </c>
@@ -4233,7 +4297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
         <v>151</v>
       </c>
@@ -4247,7 +4311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
         <v>152</v>
       </c>
@@ -4261,7 +4325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
         <v>153</v>
       </c>
@@ -4275,7 +4339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="9" t="s">
         <v>154</v>
       </c>
@@ -4289,7 +4353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="9" t="s">
         <v>155</v>
       </c>
@@ -4303,7 +4367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" s="9" t="s">
         <v>156</v>
       </c>
@@ -4317,7 +4381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" s="9" t="s">
         <v>157</v>
       </c>
@@ -4331,7 +4395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
         <v>158</v>
       </c>
@@ -4345,7 +4409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" s="9" t="s">
         <v>112</v>
       </c>
@@ -4359,7 +4423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" s="9" t="s">
         <v>163</v>
       </c>
@@ -4373,7 +4437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>164</v>
       </c>
@@ -4387,7 +4451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="9" t="s">
         <v>165</v>
       </c>
@@ -4401,7 +4465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
         <v>166</v>
       </c>
@@ -4415,7 +4479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" s="9" t="s">
         <v>167</v>
       </c>
@@ -4429,7 +4493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
         <v>168</v>
       </c>
@@ -4443,7 +4507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="9" t="s">
         <v>169</v>
       </c>
@@ -4457,7 +4521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
         <v>170</v>
       </c>
@@ -4471,7 +4535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" s="9" t="s">
         <v>325</v>
       </c>
@@ -4485,7 +4549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>172</v>
       </c>
@@ -4499,7 +4563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" s="9" t="s">
         <v>173</v>
       </c>
@@ -4513,7 +4577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>174</v>
       </c>
@@ -4527,7 +4591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" s="9" t="s">
         <v>175</v>
       </c>
@@ -4541,7 +4605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" s="9" t="s">
         <v>176</v>
       </c>
@@ -4555,7 +4619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" s="9" t="s">
         <v>177</v>
       </c>
@@ -4569,7 +4633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" s="9" t="s">
         <v>178</v>
       </c>
@@ -4583,7 +4647,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" s="9" t="s">
         <v>179</v>
       </c>
@@ -4597,7 +4661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="9" t="s">
         <v>180</v>
       </c>
@@ -4611,7 +4675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" s="9" t="s">
         <v>181</v>
       </c>
@@ -4625,7 +4689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
         <v>182</v>
       </c>
@@ -4639,7 +4703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" s="9" t="s">
         <v>190</v>
       </c>
@@ -4653,7 +4717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
         <v>191</v>
       </c>
@@ -4667,7 +4731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
         <v>192</v>
       </c>
@@ -4681,7 +4745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
         <v>193</v>
       </c>
@@ -4695,7 +4759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
         <v>194</v>
       </c>
@@ -4709,7 +4773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
         <v>189</v>
       </c>
@@ -4723,7 +4787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" s="9" t="s">
         <v>195</v>
       </c>
@@ -4737,7 +4801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
         <v>196</v>
       </c>
@@ -4751,7 +4815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" s="9" t="s">
         <v>199</v>
       </c>
@@ -4765,7 +4829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
         <v>201</v>
       </c>
@@ -4779,7 +4843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" s="9" t="s">
         <v>203</v>
       </c>
@@ -4793,7 +4857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
         <v>205</v>
       </c>
@@ -4807,7 +4871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
         <v>207</v>
       </c>
@@ -4821,7 +4885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
         <v>218</v>
       </c>
@@ -4835,7 +4899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" s="9" t="s">
         <v>221</v>
       </c>
@@ -4849,7 +4913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
         <v>224</v>
       </c>
@@ -4863,7 +4927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
         <v>228</v>
       </c>
@@ -4877,7 +4941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
         <v>219</v>
       </c>
@@ -4891,7 +4955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" s="9" t="s">
         <v>220</v>
       </c>
@@ -4905,7 +4969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
         <v>208</v>
       </c>
@@ -4919,7 +4983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
         <v>229</v>
       </c>
@@ -4933,7 +4997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
         <v>231</v>
       </c>
@@ -4947,7 +5011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" s="9" t="s">
         <v>232</v>
       </c>
@@ -4961,7 +5025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
         <v>209</v>
       </c>
@@ -4975,7 +5039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
         <v>211</v>
       </c>
@@ -4989,7 +5053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
         <v>212</v>
       </c>
@@ -5003,7 +5067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
         <v>214</v>
       </c>
@@ -5017,7 +5081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
         <v>216</v>
       </c>
@@ -5031,7 +5095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
         <v>222</v>
       </c>
@@ -5045,7 +5109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>225</v>
       </c>
@@ -5059,7 +5123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
         <v>306</v>
       </c>
@@ -5073,7 +5137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
         <v>307</v>
       </c>
@@ -5087,7 +5151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
         <v>308</v>
       </c>
@@ -5101,7 +5165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
         <v>309</v>
       </c>
@@ -5115,7 +5179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
         <v>310</v>
       </c>
@@ -5129,7 +5193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
         <v>311</v>
       </c>
@@ -5143,7 +5207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
         <v>312</v>
       </c>
@@ -5157,7 +5221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
         <v>313</v>
       </c>
@@ -5171,7 +5235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" s="9" t="s">
         <v>314</v>
       </c>
@@ -5185,7 +5249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
         <v>315</v>
       </c>
@@ -5199,7 +5263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" s="14" t="s">
         <v>317</v>
       </c>
@@ -5213,7 +5277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" s="14" t="s">
         <v>318</v>
       </c>
@@ -5227,7 +5291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" s="14" t="s">
         <v>319</v>
       </c>
@@ -5241,7 +5305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" s="14" t="s">
         <v>320</v>
       </c>
@@ -5255,7 +5319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" s="14" t="s">
         <v>321</v>
       </c>
@@ -5269,7 +5333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" s="14" t="s">
         <v>322</v>
       </c>
@@ -5283,7 +5347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" s="14" t="s">
         <v>323</v>
       </c>
@@ -5295,6 +5359,146 @@
       </c>
       <c r="D234" s="10">
         <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B235" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D235" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A236" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B236" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C236" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D236" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A237" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B237" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C237" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D237" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B238" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C238" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D238" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B239" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C239" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D239" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A240" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="B240" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D240" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A241" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B241" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D241" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="B242" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C242" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D242" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="B243" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C243" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D243" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A244" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B244" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D244" s="16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
